--- a/data/trans_dic/P36B13_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36B13_R-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,3</t>
+          <t>7,21; 11,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,77</t>
+          <t>4,94; 9,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,96</t>
+          <t>3,28; 6,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,73</t>
+          <t>1,72; 3,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,92</t>
+          <t>5,48; 7,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,58</t>
+          <t>3,43; 5,58</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 16,02</t>
+          <t>12,91; 15,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 44,87</t>
+          <t>7,13; 10,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,01</t>
+          <t>8,47; 10,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,72</t>
+          <t>3,7; 5,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 13,17</t>
+          <t>11,03; 13,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 26,44</t>
+          <t>5,71; 7,57</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,07</t>
+          <t>6,09; 11,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,52</t>
+          <t>2,93; 6,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,63</t>
+          <t>5,26; 9,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,27</t>
+          <t>2,05; 5,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,55</t>
+          <t>6,26; 9,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,51</t>
+          <t>2,7; 5,15</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,44</t>
+          <t>11,28; 13,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 35,2</t>
+          <t>6,49; 8,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,77</t>
+          <t>6,92; 8,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,18</t>
+          <t>3,27; 4,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 10,72</t>
+          <t>9,26; 10,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 19,97</t>
+          <t>5,01; 6,35</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>40763</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55200</t>
+          <t>62260</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51592; 84273</t>
+          <t>53774; 85966</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24660; 50182</t>
+          <t>28494; 55479</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33705; 58552</t>
+          <t>32204; 59415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12769; 28169</t>
+          <t>14114; 30953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96198; 136956</t>
+          <t>94762; 135029</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43212; 70760</t>
+          <t>47973; 78027</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>412612</t>
+          <t>190044</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82882</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>495495</t>
+          <t>288078</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>263756; 331215</t>
+          <t>266874; 328439</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>178023; 1026370</t>
+          <t>158740; 226804</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164180; 217965</t>
+          <t>167543; 216982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59366; 105232</t>
+          <t>79978; 118829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>443234; 532833</t>
+          <t>446440; 530107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>249690; 1194569</t>
+          <t>250643; 332676</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51597</t>
+          <t>56281</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33440; 60234</t>
+          <t>33112; 60196</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17111; 42174</t>
+          <t>20854; 47421</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28285; 52694</t>
+          <t>28802; 52245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14489; 34712</t>
+          <t>15043; 37592</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>69256; 104214</t>
+          <t>68359; 102335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37530; 71913</t>
+          <t>39024; 74407</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>476559</t>
+          <t>262909</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125733</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>602292</t>
+          <t>406619</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>379098; 451152</t>
+          <t>378611; 452917</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>239512; 1213682</t>
+          <t>228231; 306813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>244775; 307670</t>
+          <t>242747; 308220</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>99783; 152521</t>
+          <t>121441; 169727</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>639039; 735955</t>
+          <t>635880; 737117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>357808; 1416189</t>
+          <t>362552; 459608</t>
         </is>
       </c>
     </row>
